--- a/data/trans_orig/IP25A02_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP25A02_2023-Clase-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>4724</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21517</t>
+          <t>22024</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>3883</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13572</t>
+          <t>13731</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10486</t>
+          <t>10293</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28837</t>
+          <t>29283</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,32%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15371</t>
+          <t>15266</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29130</t>
+          <t>28733</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20399</t>
+          <t>19991</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37739</t>
+          <t>38638</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39858</t>
+          <t>40728</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>62000</t>
+          <t>63472</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,7%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24921</t>
+          <t>26365</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41563</t>
+          <t>42300</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36396</t>
+          <t>37519</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59375</t>
+          <t>59226</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>68416</t>
+          <t>68515</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>96048</t>
+          <t>95452</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,15%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28117</t>
+          <t>28659</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44333</t>
+          <t>44752</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40946</t>
+          <t>40717</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66864</t>
+          <t>65504</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>74451</t>
+          <t>74007</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>104976</t>
+          <t>103907</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>43,71%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4351</t>
+          <t>4311</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13220</t>
+          <t>13878</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>3553</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15409</t>
+          <t>14711</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10738</t>
+          <t>10033</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>25326</t>
+          <t>24332</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11628</t>
+          <t>12057</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24729</t>
+          <t>24162</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19191</t>
+          <t>19543</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35179</t>
+          <t>34597</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34162</t>
+          <t>34447</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55109</t>
+          <t>53971</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>28,6%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31778</t>
+          <t>31592</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47110</t>
+          <t>46982</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31571</t>
+          <t>32263</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48532</t>
+          <t>48710</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>67577</t>
+          <t>67560</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>89599</t>
+          <t>90097</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,74%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21889</t>
+          <t>21858</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36434</t>
+          <t>37101</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15148</t>
+          <t>15070</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28577</t>
+          <t>28644</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>41046</t>
+          <t>40258</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>61172</t>
+          <t>61197</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,43%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6476</t>
+          <t>6715</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>724</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7699</t>
+          <t>7152</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10500</t>
+          <t>10345</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11657</t>
+          <t>12101</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11100</t>
+          <t>11143</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24250</t>
+          <t>24158</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>16610</t>
+          <t>17144</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>32411</t>
+          <t>32094</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,74%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16478</t>
+          <t>16506</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29480</t>
+          <t>29108</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20098</t>
+          <t>20392</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34870</t>
+          <t>34667</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40485</t>
+          <t>40509</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59485</t>
+          <t>59726</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,61%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13554</t>
+          <t>13919</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25521</t>
+          <t>25847</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11389</t>
+          <t>11770</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25273</t>
+          <t>24969</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28105</t>
+          <t>28293</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45906</t>
+          <t>46597</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>40,27%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>5842</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18913</t>
+          <t>18263</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10558</t>
+          <t>10065</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25897</t>
+          <t>26416</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19594</t>
+          <t>19223</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>40644</t>
+          <t>38385</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23626</t>
+          <t>22922</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48611</t>
+          <t>47333</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26273</t>
+          <t>26927</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>46559</t>
+          <t>47255</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>55830</t>
+          <t>55754</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>86636</t>
+          <t>88528</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,41%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>55687</t>
+          <t>54721</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>104628</t>
+          <t>102774</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>83719</t>
+          <t>83988</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>113000</t>
+          <t>114495</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>146985</t>
+          <t>148860</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>208054</t>
+          <t>208337</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>48,04%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>59981</t>
+          <t>60755</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>130907</t>
+          <t>137449</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>54487</t>
+          <t>53249</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>82713</t>
+          <t>81301</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>124687</t>
+          <t>123582</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>211007</t>
+          <t>207410</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>47,82%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10951</t>
+          <t>11129</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18058</t>
+          <t>18622</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10125</t>
+          <t>9908</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>25960</t>
+          <t>26313</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17736</t>
+          <t>17607</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>35191</t>
+          <t>35219</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24149</t>
+          <t>22169</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>44252</t>
+          <t>43535</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>46920</t>
+          <t>45485</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>73457</t>
+          <t>72787</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>36583</t>
+          <t>36092</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>54008</t>
+          <t>53916</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>47863</t>
+          <t>48937</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>75502</t>
+          <t>76412</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>92561</t>
+          <t>91874</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>123888</t>
+          <t>126181</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>45,2%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>32428</t>
+          <t>31954</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>49532</t>
+          <t>50015</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>41033</t>
+          <t>41849</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>77815</t>
+          <t>76688</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>78459</t>
+          <t>79723</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>120166</t>
+          <t>120323</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,1%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3779</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13792</t>
+          <t>13149</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1712</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11376</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7180</t>
+          <t>7003</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>19950</t>
+          <t>21124</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>11238</t>
+          <t>11476</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>24155</t>
+          <t>23867</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>14533</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>29405</t>
+          <t>30369</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>30164</t>
+          <t>30105</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>49059</t>
+          <t>49236</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,79%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>19906</t>
+          <t>19618</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34334</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>21852</t>
+          <t>21636</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>36711</t>
+          <t>36482</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>46328</t>
+          <t>46422</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>66201</t>
+          <t>67480</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>49,05%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>10529</t>
+          <t>10566</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>22167</t>
+          <t>22353</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>8708</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>19943</t>
+          <t>20267</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>22662</t>
+          <t>22508</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>39390</t>
+          <t>38759</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,18%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>35100</t>
+          <t>34078</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>61101</t>
+          <t>59986</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>38476</t>
+          <t>37928</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>65303</t>
+          <t>66446</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>78849</t>
+          <t>78665</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>115699</t>
+          <t>117661</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>102862</t>
+          <t>103811</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>145853</t>
+          <t>144134</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>144161</t>
+          <t>141845</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>185603</t>
+          <t>186389</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>258453</t>
+          <t>259999</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>317214</t>
+          <t>319649</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,95%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>214597</t>
+          <t>214104</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>277016</t>
+          <t>278045</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>280370</t>
+          <t>277867</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>332764</t>
+          <t>332375</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>515577</t>
+          <t>512027</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>595776</t>
+          <t>595898</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,79%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>196770</t>
+          <t>197288</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>288003</t>
+          <t>286756</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>199313</t>
+          <t>201090</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>255750</t>
+          <t>258981</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>409237</t>
+          <t>410902</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>515287</t>
+          <t>513414</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>36,87%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP25A02_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP25A02_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9874</t>
+          <t>6716</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4724</t>
+          <t>3550</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22024</t>
+          <t>12107</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7567</t>
+          <t>7639</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>3318</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13731</t>
+          <t>12773</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>17441</t>
+          <t>14355</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10293</t>
+          <t>8728</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29283</t>
+          <t>21448</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>28754</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>19982</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>37399</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>23,52%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>16,35%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>30,59%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>21278</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>15266</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>28733</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>21,02%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>15,08%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>28,39%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28937</t>
+          <t>21439</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19991</t>
+          <t>14861</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38638</t>
+          <t>28398</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>50215</t>
+          <t>50193</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40728</t>
+          <t>39570</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>63472</t>
+          <t>61223</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>47053</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>37443</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>57099</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>38,49%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>30,63%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>46,71%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>33812</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>26365</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>42300</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>33,41%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>26,05%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>41,8%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>48462</t>
+          <t>34896</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37519</t>
+          <t>26910</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59226</t>
+          <t>42714</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>82273</t>
+          <t>81949</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>68515</t>
+          <t>70539</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>95452</t>
+          <t>96157</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>43,3%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>39729</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>30105</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>48496</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>32,5%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>24,63%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>39,67%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>36245</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>28659</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>44752</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>35,81%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>28,32%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>44,22%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>51552</t>
+          <t>35858</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40717</t>
+          <t>28643</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65504</t>
+          <t>44900</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>87797</t>
+          <t>75586</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>74007</t>
+          <t>64185</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>103907</t>
+          <t>88364</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>39,79%</t>
         </is>
       </c>
     </row>
@@ -1172,57 +1172,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>122252</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>122252</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>122252</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>101208</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>101208</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>101208</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>136518</t>
+          <t>99832</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>136518</t>
+          <t>99832</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>136518</t>
+          <t>99832</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>237726</t>
+          <t>222084</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>237726</t>
+          <t>222084</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>237726</t>
+          <t>222084</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>7525</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>3564</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>14385</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>8,23%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>3,9%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>15,74%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>8060</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>4311</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>13878</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>8,65%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>4,63%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>14,9%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8061</t>
+          <t>8336</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3553</t>
+          <t>4472</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14711</t>
+          <t>14025</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>16121</t>
+          <t>15861</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10033</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>24332</t>
+          <t>24732</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>25558</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18428</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>33883</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>27,96%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>20,16%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>37,07%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>17268</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>12057</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>24162</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>18,54%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,94%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>25,94%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>26646</t>
+          <t>18148</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19543</t>
+          <t>12076</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34597</t>
+          <t>26028</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>43915</t>
+          <t>43706</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34447</t>
+          <t>34904</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53971</t>
+          <t>54786</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>29,38%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>38423</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>30459</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>47639</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>42,04%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>33,33%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>52,12%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>39194</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>31592</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>46982</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>42,07%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>33,91%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>50,43%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>39618</t>
+          <t>40102</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32263</t>
+          <t>32155</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48710</t>
+          <t>48701</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>78813</t>
+          <t>78525</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>67560</t>
+          <t>66671</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>90097</t>
+          <t>90811</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>48,7%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>19892</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>13890</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>27603</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>21,76%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>15,2%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>30,2%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>28635</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>21858</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>37101</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>30,74%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>23,46%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>39,83%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21247</t>
+          <t>28498</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15070</t>
+          <t>20968</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28644</t>
+          <t>36218</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>49882</t>
+          <t>48390</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>40258</t>
+          <t>39088</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>61197</t>
+          <t>59307</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>31,8%</t>
         </is>
       </c>
     </row>
@@ -1741,57 +1741,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>93157</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>93157</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>93157</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>95083</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>95083</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>95083</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>188730</t>
+          <t>186481</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>188730</t>
+          <t>186481</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>188730</t>
+          <t>186481</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1735</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>406</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5036</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3,05%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>8,84%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2873</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1076</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6715</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5,54%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>12,95%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2620</t>
+          <t>2723</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>913</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7152</t>
+          <t>6347</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5493</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>2084</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10345</t>
+          <t>8682</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -1971,72 +1971,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>15618</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>10212</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>22378</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>27,43%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>17,93%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>39,3%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>6794</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>3574</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>12101</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>13,1%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>6,89%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>23,33%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17017</t>
+          <t>7266</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11143</t>
+          <t>3751</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24158</t>
+          <t>12522</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>23811</t>
+          <t>22884</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>17144</t>
+          <t>15838</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>32094</t>
+          <t>31555</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>28,58%</t>
         </is>
       </c>
     </row>
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>25749</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>19119</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>32290</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>45,22%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>33,58%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>56,71%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>22612</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>16506</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>29108</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>43,6%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>31,83%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>56,13%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>27224</t>
+          <t>23634</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20392</t>
+          <t>17408</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34667</t>
+          <t>31155</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>49836</t>
+          <t>49383</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40509</t>
+          <t>38883</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59726</t>
+          <t>57806</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>52,35%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>13839</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>9218</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>20181</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>24,3%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>16,19%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>35,44%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>19582</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>13919</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>25847</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>37,76%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>26,84%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>49,84%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16992</t>
+          <t>19859</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11770</t>
+          <t>13871</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24969</t>
+          <t>27238</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>36575</t>
+          <t>33698</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28293</t>
+          <t>25781</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>46597</t>
+          <t>42923</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>38,87%</t>
         </is>
       </c>
     </row>
@@ -2310,57 +2310,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2427,72 +2427,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>16374</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>9622</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>25676</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>8,13%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>4,78%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>12,74%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>11435</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>5842</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>18263</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>5,29%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>8,45%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17002</t>
+          <t>11296</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10065</t>
+          <t>6545</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26416</t>
+          <t>18146</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>28438</t>
+          <t>27670</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19223</t>
+          <t>18981</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38385</t>
+          <t>37503</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -2540,72 +2540,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>31928</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>23471</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>42064</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>15,85%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>11,65%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>20,88%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>36349</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>22922</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>47333</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>16,83%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>10,61%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>21,91%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>35669</t>
+          <t>35349</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26927</t>
+          <t>27091</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>47255</t>
+          <t>44449</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>72018</t>
+          <t>67276</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>55754</t>
+          <t>54159</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>88528</t>
+          <t>81250</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>21,49%</t>
         </is>
       </c>
     </row>
@@ -2653,72 +2653,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>91874</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>78772</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>106394</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>45,6%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>39,1%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>52,81%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>84904</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>54721</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>102774</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>39,3%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>25,33%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>47,58%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>98371</t>
+          <t>73416</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>83988</t>
+          <t>62638</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>114495</t>
+          <t>85509</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>183275</t>
+          <t>165291</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>148860</t>
+          <t>147721</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>208337</t>
+          <t>185367</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>49,02%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>83325</t>
+          <t>61294</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>60755</t>
+          <t>49043</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>137449</t>
+          <t>74910</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>66652</t>
+          <t>56612</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53249</t>
+          <t>46237</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>81301</t>
+          <t>67531</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>149977</t>
+          <t>117906</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>123582</t>
+          <t>102058</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>207410</t>
+          <t>136955</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>36,22%</t>
         </is>
       </c>
     </row>
@@ -2879,57 +2879,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>201470</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>201470</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>201470</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>216014</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>216014</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>216014</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>217694</t>
+          <t>176673</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>217694</t>
+          <t>176673</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>217694</t>
+          <t>176673</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>433708</t>
+          <t>378143</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>433708</t>
+          <t>378143</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>433708</t>
+          <t>378143</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2996,72 +2996,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>8845</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>4588</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>14726</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>5,98%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>9,95%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>5938</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>2972</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>11129</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>5,08%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>9,52%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>5703</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18622</t>
+          <t>10734</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>14548</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9908</t>
+          <t>9171</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>26313</t>
+          <t>21680</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -3109,72 +3109,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>32214</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>23423</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>43825</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>21,77%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>15,83%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>29,62%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>25400</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>17607</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>35219</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>21,72%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>15,06%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>30,12%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>33222</t>
+          <t>23763</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22169</t>
+          <t>17366</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>43535</t>
+          <t>31692</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>58622</t>
+          <t>55976</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>45485</t>
+          <t>42691</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>72787</t>
+          <t>69207</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -3222,72 +3222,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>57635</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>43854</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>69869</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>38,96%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>29,64%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>47,23%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>45287</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>36092</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>53916</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>38,73%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>30,87%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>46,11%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>63363</t>
+          <t>46861</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>48937</t>
+          <t>37936</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>76412</t>
+          <t>55964</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>108650</t>
+          <t>104496</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>91874</t>
+          <t>89092</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>126181</t>
+          <t>120825</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,74%</t>
         </is>
       </c>
     </row>
@@ -3335,72 +3335,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>49246</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>37311</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>68791</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>33,29%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>25,22%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>46,5%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>40297</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>31954</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>50015</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>34,46%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>27,33%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>42,78%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>55151</t>
+          <t>39871</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>41849</t>
+          <t>31702</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>76688</t>
+          <t>48373</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>95449</t>
+          <t>89116</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>79723</t>
+          <t>75110</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>120323</t>
+          <t>107966</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>40,87%</t>
         </is>
       </c>
     </row>
@@ -3448,57 +3448,57 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>147940</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>147940</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>147940</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>116923</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>116923</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>116923</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>162259</t>
+          <t>116197</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>162259</t>
+          <t>116197</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>162259</t>
+          <t>116197</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>279182</t>
+          <t>264136</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>279182</t>
+          <t>264136</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>279182</t>
+          <t>264136</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3565,72 +3565,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>4767</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>1677</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>10899</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>7,17%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>16,4%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>7444</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>3159</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>13149</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>11,04%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>19,51%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>4934</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>3854</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11527</t>
+          <t>14238</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>12378</t>
+          <t>12806</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7003</t>
+          <t>7255</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>21124</t>
+          <t>20665</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -3678,72 +3678,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>21306</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>14507</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>28771</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>32,06%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>21,83%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>43,29%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>16900</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>11476</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>23867</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>25,07%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>17,02%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>35,4%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>22046</t>
+          <t>16874</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>15896</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>30369</t>
+          <t>23129</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>38946</t>
+          <t>38180</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>30105</t>
+          <t>29736</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>49236</t>
+          <t>47959</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,36%</t>
         </is>
       </c>
     </row>
@@ -3791,72 +3791,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>27814</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>20451</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>34629</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>41,85%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>30,77%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>52,11%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>27132</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>19618</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>34334</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>40,25%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>29,1%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>50,93%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>29125</t>
+          <t>28202</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>21636</t>
+          <t>21221</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>36482</t>
+          <t>36262</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>56258</t>
+          <t>56017</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>46422</t>
+          <t>46546</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>67480</t>
+          <t>66990</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>49,39%</t>
         </is>
       </c>
     </row>
@@ -3904,72 +3904,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>12571</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>7808</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>18083</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>18,92%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>11,75%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>27,21%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>15937</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>10566</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>22353</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>23,64%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>15,67%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>33,16%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>14046</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>8708</t>
+          <t>10666</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>20267</t>
+          <t>23791</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>29983</t>
+          <t>28622</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>22508</t>
+          <t>21786</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>38759</t>
+          <t>37736</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>27,82%</t>
         </is>
       </c>
     </row>
@@ -4017,57 +4017,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>66459</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>66459</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>66459</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>67413</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>67413</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>67413</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>70152</t>
+          <t>69166</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>70152</t>
+          <t>69166</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>70152</t>
+          <t>69166</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>137565</t>
+          <t>135625</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>137565</t>
+          <t>135625</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>137565</t>
+          <t>135625</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4134,72 +4134,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>45962</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>35081</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>60662</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>5,11%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>8,84%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>45624</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>34078</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>59986</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>9,28%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>50708</t>
+          <t>43736</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>37928</t>
+          <t>33270</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>66446</t>
+          <t>56515</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,17 +4209,17 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>96332</t>
+          <t>89699</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>78665</t>
+          <t>73423</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>117661</t>
+          <t>108118</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -4247,72 +4247,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>155377</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>135642</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>175837</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>22,63%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>19,76%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>25,62%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>123990</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>103811</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>144134</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>19,18%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>16,06%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>22,29%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>163537</t>
+          <t>122838</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>141845</t>
+          <t>107332</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>186389</t>
+          <t>140429</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>287527</t>
+          <t>278215</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>259999</t>
+          <t>253761</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>319649</t>
+          <t>306381</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,62%</t>
         </is>
       </c>
     </row>
@@ -4360,72 +4360,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>288549</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>264851</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>313594</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>42,03%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>38,58%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>45,68%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>356</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>252942</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>214104</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>278045</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>39,12%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>33,11%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>43,0%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>393</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>306162</t>
+          <t>247110</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>277867</t>
+          <t>228074</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>332375</t>
+          <t>269283</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>559104</t>
+          <t>535660</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>512027</t>
+          <t>503543</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>595898</t>
+          <t>568104</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>43,81%</t>
         </is>
       </c>
     </row>
@@ -4473,72 +4473,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>196570</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>174827</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>222235</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>28,64%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>25,47%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>32,37%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>314</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>224022</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>197288</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>286756</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>34,65%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>30,51%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>44,35%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>225641</t>
+          <t>196749</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>201090</t>
+          <t>176038</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>258981</t>
+          <t>216324</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>449662</t>
+          <t>393319</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>410902</t>
+          <t>364933</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>513414</t>
+          <t>427427</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>32,96%</t>
         </is>
       </c>
     </row>
@@ -4586,57 +4586,57 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>954</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>686459</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>686459</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>686459</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>646578</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>646578</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>646578</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>954</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>746048</t>
+          <t>610433</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>746048</t>
+          <t>610433</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>746048</t>
+          <t>610433</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1392625</t>
+          <t>1296892</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1392625</t>
+          <t>1296892</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1392625</t>
+          <t>1296892</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
